--- a/database_penyimpanan_aman/database_master_referensi.xlsx
+++ b/database_penyimpanan_aman/database_master_referensi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB9158F-E552-4AE7-950E-C2166D4FF671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9826E160-3F8F-4596-9386-8DA4EF6FE5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/database_penyimpanan_aman/database_master_referensi.xlsx
+++ b/database_penyimpanan_aman/database_master_referensi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9826E160-3F8F-4596-9386-8DA4EF6FE5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2909EAC7-3F15-4FCB-A62A-1FB72964A602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1449,7 +1449,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1475,13 +1485,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1789,7 +1802,7 @@
     <col min="2" max="2" width="17.265625" customWidth="1"/>
     <col min="3" max="3" width="27.06640625" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16.3984375" customWidth="1"/>
+    <col min="5" max="5" width="23.46484375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -1805,7 +1818,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1825,7 +1838,7 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>131224000</v>
       </c>
       <c r="F2" t="s">
@@ -1845,7 +1858,7 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>62818000</v>
       </c>
       <c r="F3" t="s">
@@ -1865,7 +1878,7 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>189241000</v>
       </c>
       <c r="F4" t="s">
@@ -1885,7 +1898,7 @@
       <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>75538000</v>
       </c>
       <c r="F5" t="s">
@@ -1905,7 +1918,7 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>78225000</v>
       </c>
       <c r="F6" t="s">
@@ -1925,7 +1938,7 @@
       <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>1936000</v>
       </c>
       <c r="F7" t="s">
@@ -1945,7 +1958,7 @@
       <c r="D8" t="s">
         <v>17</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>4746000</v>
       </c>
       <c r="F8" t="s">
@@ -1965,7 +1978,7 @@
       <c r="D9" t="s">
         <v>17</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>5340000</v>
       </c>
       <c r="F9" t="s">
@@ -1985,7 +1998,7 @@
       <c r="D10" t="s">
         <v>17</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>4231000</v>
       </c>
       <c r="F10" t="s">
@@ -2005,7 +2018,7 @@
       <c r="D11" t="s">
         <v>17</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>2215000</v>
       </c>
       <c r="F11" t="s">
@@ -2025,7 +2038,7 @@
       <c r="D12" t="s">
         <v>9</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>210000000</v>
       </c>
       <c r="F12" t="s">
@@ -2045,7 +2058,7 @@
       <c r="D13" t="s">
         <v>9</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>350000000</v>
       </c>
       <c r="F13" t="s">
@@ -2065,7 +2078,7 @@
       <c r="D14" t="s">
         <v>9</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>80000000</v>
       </c>
       <c r="F14" t="s">
@@ -2085,7 +2098,7 @@
       <c r="D15" t="s">
         <v>9</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>75000000</v>
       </c>
       <c r="F15" t="s">
@@ -2105,7 +2118,7 @@
       <c r="D16" t="s">
         <v>9</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>75000000</v>
       </c>
       <c r="F16" t="s">
@@ -2125,7 +2138,7 @@
       <c r="D17" t="s">
         <v>28</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>400000000</v>
       </c>
       <c r="F17" t="s">
@@ -2145,7 +2158,7 @@
       <c r="D18" t="s">
         <v>28</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>300000000</v>
       </c>
       <c r="F18" t="s">
@@ -2165,7 +2178,7 @@
       <c r="D19" t="s">
         <v>31</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>7500000</v>
       </c>
       <c r="F19" t="s">
@@ -2185,7 +2198,7 @@
       <c r="D20" t="s">
         <v>31</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>7500000</v>
       </c>
       <c r="F20" t="s">
@@ -2205,7 +2218,7 @@
       <c r="D21" t="s">
         <v>31</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>8500000</v>
       </c>
       <c r="F21" t="s">
@@ -2225,7 +2238,7 @@
       <c r="D22" t="s">
         <v>17</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>1197000</v>
       </c>
       <c r="F22" t="s">
@@ -2245,7 +2258,7 @@
       <c r="D23" t="s">
         <v>28</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>598500</v>
       </c>
       <c r="F23" t="s">
@@ -2265,7 +2278,7 @@
       <c r="D24" t="s">
         <v>40</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>500000</v>
       </c>
       <c r="F24" t="s">
@@ -2285,7 +2298,7 @@
       <c r="D25" t="s">
         <v>40</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>850000</v>
       </c>
       <c r="F25" t="s">
@@ -2305,7 +2318,7 @@
       <c r="D26" t="s">
         <v>40</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>500000</v>
       </c>
       <c r="F26" t="s">
@@ -2325,7 +2338,7 @@
       <c r="D27" t="s">
         <v>40</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>750000</v>
       </c>
       <c r="F27" t="s">
@@ -2345,7 +2358,7 @@
       <c r="D28" t="s">
         <v>40</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>200000</v>
       </c>
       <c r="F28" t="s">
@@ -2365,7 +2378,7 @@
       <c r="D29" t="s">
         <v>40</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>100000</v>
       </c>
       <c r="F29" t="s">
@@ -2385,7 +2398,7 @@
       <c r="D30" t="s">
         <v>40</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>150000</v>
       </c>
       <c r="F30" t="s">
@@ -2405,7 +2418,7 @@
       <c r="D31" t="s">
         <v>40</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="1">
         <v>15000</v>
       </c>
       <c r="F31" t="s">
@@ -2425,7 +2438,7 @@
       <c r="D32" t="s">
         <v>40</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1">
         <v>50000</v>
       </c>
       <c r="F32" t="s">
@@ -2445,7 +2458,7 @@
       <c r="D33" t="s">
         <v>40</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="1">
         <v>250000</v>
       </c>
       <c r="F33" t="s">
@@ -2465,7 +2478,7 @@
       <c r="D34" t="s">
         <v>40</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="1">
         <v>3000000</v>
       </c>
       <c r="F34" t="s">
@@ -2485,7 +2498,7 @@
       <c r="D35" t="s">
         <v>40</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="1">
         <v>600000</v>
       </c>
       <c r="F35" t="s">
@@ -2505,7 +2518,7 @@
       <c r="D36" t="s">
         <v>40</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="1">
         <v>260000</v>
       </c>
       <c r="F36" t="s">
@@ -2525,7 +2538,7 @@
       <c r="D37" t="s">
         <v>40</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="1">
         <v>3500000</v>
       </c>
       <c r="F37" t="s">
@@ -2545,7 +2558,7 @@
       <c r="D38" t="s">
         <v>40</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="1">
         <v>30000000</v>
       </c>
       <c r="F38" t="s">
@@ -2565,7 +2578,7 @@
       <c r="D39" t="s">
         <v>40</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="1">
         <v>25000000</v>
       </c>
       <c r="F39" t="s">
@@ -2585,7 +2598,7 @@
       <c r="D40" t="s">
         <v>40</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="1">
         <v>25000000</v>
       </c>
       <c r="F40" t="s">
@@ -2605,7 +2618,7 @@
       <c r="D41" t="s">
         <v>40</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="1">
         <v>5000000</v>
       </c>
       <c r="F41" t="s">
@@ -2625,7 +2638,7 @@
       <c r="D42" t="s">
         <v>40</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="1">
         <v>6750000</v>
       </c>
       <c r="F42" t="s">
@@ -2645,7 +2658,7 @@
       <c r="D43" t="s">
         <v>40</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="1">
         <v>2500000</v>
       </c>
       <c r="F43" t="s">
@@ -2665,7 +2678,7 @@
       <c r="D44" t="s">
         <v>40</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="1">
         <v>3250000</v>
       </c>
       <c r="F44" t="s">
@@ -2685,7 +2698,7 @@
       <c r="D45" t="s">
         <v>40</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="1">
         <v>2500000</v>
       </c>
       <c r="F45" t="s">
@@ -2705,7 +2718,7 @@
       <c r="D46" t="s">
         <v>40</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="1">
         <v>250000</v>
       </c>
       <c r="F46" t="s">
@@ -2725,7 +2738,7 @@
       <c r="D47" t="s">
         <v>40</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="1">
         <v>2250000</v>
       </c>
       <c r="F47" t="s">
@@ -2745,7 +2758,7 @@
       <c r="D48" t="s">
         <v>40</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="1">
         <v>275000</v>
       </c>
       <c r="F48" t="s">
@@ -2765,7 +2778,7 @@
       <c r="D49" t="s">
         <v>66</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="1">
         <v>1000000</v>
       </c>
       <c r="F49" t="s">
@@ -2785,7 +2798,7 @@
       <c r="D50" t="s">
         <v>68</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="1">
         <v>250000</v>
       </c>
       <c r="F50" t="s">
@@ -2805,7 +2818,7 @@
       <c r="D51" t="s">
         <v>68</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="1">
         <v>75000</v>
       </c>
       <c r="F51" t="s">
@@ -2825,7 +2838,7 @@
       <c r="D52" t="s">
         <v>68</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="1">
         <v>75000</v>
       </c>
       <c r="F52" t="s">
@@ -2845,7 +2858,7 @@
       <c r="D53" t="s">
         <v>71</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="1">
         <v>75000</v>
       </c>
       <c r="F53" t="s">
@@ -2865,7 +2878,7 @@
       <c r="D54" t="s">
         <v>71</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="1">
         <v>75000</v>
       </c>
       <c r="F54" t="s">
@@ -2885,7 +2898,7 @@
       <c r="D55" t="s">
         <v>68</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="1">
         <v>10000000</v>
       </c>
       <c r="F55" t="s">
@@ -2905,7 +2918,7 @@
       <c r="D56" t="s">
         <v>9</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="1">
         <v>5000000</v>
       </c>
       <c r="F56" t="s">
@@ -2925,7 +2938,7 @@
       <c r="D57" t="s">
         <v>9</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="1">
         <v>30000000</v>
       </c>
       <c r="F57" t="s">
@@ -2945,7 +2958,7 @@
       <c r="D58" t="s">
         <v>9</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="1">
         <v>30000000</v>
       </c>
       <c r="F58" t="s">
@@ -2965,7 +2978,7 @@
       <c r="D59" t="s">
         <v>77</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="1">
         <v>500000</v>
       </c>
       <c r="F59" t="s">
@@ -2985,7 +2998,7 @@
       <c r="D60" t="s">
         <v>77</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="1">
         <v>500000</v>
       </c>
       <c r="F60" t="s">
@@ -3005,7 +3018,7 @@
       <c r="D61" t="s">
         <v>77</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="1">
         <v>65000000</v>
       </c>
       <c r="F61" t="s">
@@ -3025,7 +3038,7 @@
       <c r="D62" t="s">
         <v>9</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="1">
         <v>65000000</v>
       </c>
       <c r="F62" t="s">
@@ -3045,7 +3058,7 @@
       <c r="D63" t="s">
         <v>17</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="1">
         <v>1600000</v>
       </c>
       <c r="F63" t="s">
@@ -3065,7 +3078,7 @@
       <c r="D64" t="s">
         <v>17</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="1">
         <v>1600000</v>
       </c>
       <c r="F64" t="s">
@@ -3085,7 +3098,7 @@
       <c r="D65" t="s">
         <v>17</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="1">
         <v>6900000</v>
       </c>
       <c r="F65" t="s">
@@ -3105,7 +3118,7 @@
       <c r="D66" t="s">
         <v>17</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="1">
         <v>6900000</v>
       </c>
       <c r="F66" t="s">
@@ -3125,7 +3138,7 @@
       <c r="D67" t="s">
         <v>68</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="1">
         <v>6900000</v>
       </c>
       <c r="F67" t="s">
@@ -3145,7 +3158,7 @@
       <c r="D68" t="s">
         <v>68</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="1">
         <v>5290000</v>
       </c>
       <c r="F68" t="s">
@@ -3165,7 +3178,7 @@
       <c r="D69" t="s">
         <v>68</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="1">
         <v>5750000</v>
       </c>
       <c r="F69" t="s">
@@ -3185,7 +3198,7 @@
       <c r="D70" t="s">
         <v>68</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="1">
         <v>7000000</v>
       </c>
       <c r="F70" t="s">
@@ -3205,7 +3218,7 @@
       <c r="D71" t="s">
         <v>68</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="1">
         <v>7130000</v>
       </c>
       <c r="F71" t="s">
@@ -3225,7 +3238,7 @@
       <c r="D72" t="s">
         <v>68</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="1">
         <v>7590000</v>
       </c>
       <c r="F72" t="s">
@@ -3245,7 +3258,7 @@
       <c r="D73" t="s">
         <v>68</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="1">
         <v>7000000</v>
       </c>
       <c r="F73" t="s">
@@ -3265,7 +3278,7 @@
       <c r="D74" t="s">
         <v>68</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="1">
         <v>6900000</v>
       </c>
       <c r="F74" t="s">
@@ -3285,7 +3298,7 @@
       <c r="D75" t="s">
         <v>68</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="1">
         <v>7000000</v>
       </c>
       <c r="F75" t="s">
@@ -3305,7 +3318,7 @@
       <c r="D76" t="s">
         <v>68</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="1">
         <v>8250000</v>
       </c>
       <c r="F76" t="s">
@@ -3325,7 +3338,7 @@
       <c r="D77" t="s">
         <v>68</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="1">
         <v>7000000</v>
       </c>
       <c r="F77" t="s">
@@ -3345,7 +3358,7 @@
       <c r="D78" t="s">
         <v>68</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="1">
         <v>7000000</v>
       </c>
       <c r="F78" t="s">
@@ -3365,7 +3378,7 @@
       <c r="D79" t="s">
         <v>68</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="1">
         <v>5060000</v>
       </c>
       <c r="F79" t="s">
@@ -3385,7 +3398,7 @@
       <c r="D80" t="s">
         <v>68</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="1">
         <v>5980000</v>
       </c>
       <c r="F80" t="s">
@@ -3405,7 +3418,7 @@
       <c r="D81" t="s">
         <v>68</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="1">
         <v>5290000</v>
       </c>
       <c r="F81" t="s">
@@ -3425,7 +3438,7 @@
       <c r="D82" t="s">
         <v>68</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="1">
         <v>5060000</v>
       </c>
       <c r="F82" t="s">
@@ -3445,7 +3458,7 @@
       <c r="D83" t="s">
         <v>68</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="1">
         <v>5520000</v>
       </c>
       <c r="F83" t="s">
@@ -3465,7 +3478,7 @@
       <c r="D84" t="s">
         <v>68</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="1">
         <v>5520000</v>
       </c>
       <c r="F84" t="s">
@@ -3485,7 +3498,7 @@
       <c r="D85" t="s">
         <v>68</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="1">
         <v>5060000</v>
       </c>
       <c r="F85" t="s">
@@ -3505,7 +3518,7 @@
       <c r="D86" t="s">
         <v>68</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="1">
         <v>5290000</v>
       </c>
       <c r="F86" t="s">
@@ -3525,7 +3538,7 @@
       <c r="D87" t="s">
         <v>68</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="1">
         <v>5980000</v>
       </c>
       <c r="F87" t="s">
@@ -3545,7 +3558,7 @@
       <c r="D88" t="s">
         <v>68</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="1">
         <v>5980000</v>
       </c>
       <c r="F88" t="s">
@@ -3565,7 +3578,7 @@
       <c r="D89" t="s">
         <v>68</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="1">
         <v>5980000</v>
       </c>
       <c r="F89" t="s">
@@ -3585,7 +3598,7 @@
       <c r="D90" t="s">
         <v>68</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="1">
         <v>5520000</v>
       </c>
       <c r="F90" t="s">
@@ -3605,7 +3618,7 @@
       <c r="D91" t="s">
         <v>68</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="1">
         <v>6440000</v>
       </c>
       <c r="F91" t="s">
@@ -3625,7 +3638,7 @@
       <c r="D92" t="s">
         <v>68</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="1">
         <v>5060000</v>
       </c>
       <c r="F92" t="s">
@@ -3645,7 +3658,7 @@
       <c r="D93" t="s">
         <v>68</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="1">
         <v>5060000</v>
       </c>
       <c r="F93" t="s">
@@ -3665,7 +3678,7 @@
       <c r="D94" t="s">
         <v>68</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="1">
         <v>5290000</v>
       </c>
       <c r="F94" t="s">
@@ -3685,7 +3698,7 @@
       <c r="D95" t="s">
         <v>68</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="1">
         <v>5060000</v>
       </c>
       <c r="F95" t="s">
@@ -3705,7 +3718,7 @@
       <c r="D96" t="s">
         <v>68</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="1">
         <v>5290000</v>
       </c>
       <c r="F96" t="s">
@@ -3725,7 +3738,7 @@
       <c r="D97" t="s">
         <v>68</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="1">
         <v>6440000</v>
       </c>
       <c r="F97" t="s">
@@ -3745,7 +3758,7 @@
       <c r="D98" t="s">
         <v>68</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="1">
         <v>5520000</v>
       </c>
       <c r="F98" t="s">
@@ -3765,7 +3778,7 @@
       <c r="D99" t="s">
         <v>68</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="1">
         <v>5520000</v>
       </c>
       <c r="F99" t="s">
@@ -3785,7 +3798,7 @@
       <c r="D100" t="s">
         <v>68</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="1">
         <v>5520000</v>
       </c>
       <c r="F100" t="s">
@@ -3805,7 +3818,7 @@
       <c r="D101" t="s">
         <v>68</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="1">
         <v>6440000</v>
       </c>
       <c r="F101" t="s">
@@ -3825,7 +3838,7 @@
       <c r="D102" t="s">
         <v>68</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="1">
         <v>5290000</v>
       </c>
       <c r="F102" t="s">
@@ -3845,7 +3858,7 @@
       <c r="D103" t="s">
         <v>68</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="1">
         <v>5290000</v>
       </c>
       <c r="F103" t="s">
@@ -3865,7 +3878,7 @@
       <c r="D104" t="s">
         <v>68</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="1">
         <v>5290000</v>
       </c>
       <c r="F104" t="s">
@@ -3885,7 +3898,7 @@
       <c r="D105" t="s">
         <v>68</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="1">
         <v>5290000</v>
       </c>
       <c r="F105" t="s">
@@ -3905,7 +3918,7 @@
       <c r="D106" t="s">
         <v>68</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="1">
         <v>5290000</v>
       </c>
       <c r="F106" t="s">
@@ -3925,7 +3938,7 @@
       <c r="D107" t="s">
         <v>68</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="1">
         <v>5290000</v>
       </c>
       <c r="F107" t="s">
@@ -3945,7 +3958,7 @@
       <c r="D108" t="s">
         <v>68</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="1">
         <v>5520000</v>
       </c>
       <c r="F108" t="s">
@@ -3965,7 +3978,7 @@
       <c r="D109" t="s">
         <v>68</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="1">
         <v>6440000</v>
       </c>
       <c r="F109" t="s">
@@ -3985,7 +3998,7 @@
       <c r="D110" t="s">
         <v>68</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="1">
         <v>5060000</v>
       </c>
       <c r="F110" t="s">
@@ -4005,7 +4018,7 @@
       <c r="D111" t="s">
         <v>68</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="1">
         <v>5060000</v>
       </c>
       <c r="F111" t="s">
@@ -4025,7 +4038,7 @@
       <c r="D112" t="s">
         <v>68</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="1">
         <v>5290000</v>
       </c>
       <c r="F112" t="s">
@@ -4045,7 +4058,7 @@
       <c r="D113" t="s">
         <v>68</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="1">
         <v>5750000</v>
       </c>
       <c r="F113" t="s">
@@ -4065,7 +4078,7 @@
       <c r="D114" t="s">
         <v>68</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="1">
         <v>5290000</v>
       </c>
       <c r="F114" t="s">
@@ -4085,7 +4098,7 @@
       <c r="D115" t="s">
         <v>68</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="1">
         <v>5290000</v>
       </c>
       <c r="F115" t="s">
@@ -4105,7 +4118,7 @@
       <c r="D116" t="s">
         <v>68</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="1">
         <v>5290000</v>
       </c>
       <c r="F116" t="s">
@@ -4125,7 +4138,7 @@
       <c r="D117" t="s">
         <v>68</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="1">
         <v>5290000</v>
       </c>
       <c r="F117" t="s">
@@ -4145,7 +4158,7 @@
       <c r="D118" t="s">
         <v>68</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="1">
         <v>5290000</v>
       </c>
       <c r="F118" t="s">
@@ -4165,7 +4178,7 @@
       <c r="D119" t="s">
         <v>68</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="1">
         <v>5520000</v>
       </c>
       <c r="F119" t="s">
@@ -4185,7 +4198,7 @@
       <c r="D120" t="s">
         <v>68</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="1">
         <v>5290000</v>
       </c>
       <c r="F120" t="s">
@@ -4205,7 +4218,7 @@
       <c r="D121" t="s">
         <v>68</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="1">
         <v>5290000</v>
       </c>
       <c r="F121" t="s">
@@ -4225,7 +4238,7 @@
       <c r="D122" t="s">
         <v>68</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="1">
         <v>5060000</v>
       </c>
       <c r="F122" t="s">
@@ -4245,7 +4258,7 @@
       <c r="D123" t="s">
         <v>68</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="1">
         <v>5980000</v>
       </c>
       <c r="F123" t="s">
@@ -4265,7 +4278,7 @@
       <c r="D124" t="s">
         <v>68</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="1">
         <v>5290000</v>
       </c>
       <c r="F124" t="s">
@@ -4285,7 +4298,7 @@
       <c r="D125" t="s">
         <v>68</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="1">
         <v>5290000</v>
       </c>
       <c r="F125" t="s">
@@ -4305,7 +4318,7 @@
       <c r="D126" t="s">
         <v>68</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="1">
         <v>5290000</v>
       </c>
       <c r="F126" t="s">
@@ -4325,7 +4338,7 @@
       <c r="D127" t="s">
         <v>68</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="1">
         <v>5290000</v>
       </c>
       <c r="F127" t="s">
@@ -4345,7 +4358,7 @@
       <c r="D128" t="s">
         <v>68</v>
       </c>
-      <c r="E128">
+      <c r="E128" s="1">
         <v>5750000</v>
       </c>
       <c r="F128" t="s">
@@ -4365,7 +4378,7 @@
       <c r="D129" t="s">
         <v>68</v>
       </c>
-      <c r="E129">
+      <c r="E129" s="1">
         <v>6670000</v>
       </c>
       <c r="F129" t="s">
@@ -4385,7 +4398,7 @@
       <c r="D130" t="s">
         <v>68</v>
       </c>
-      <c r="E130">
+      <c r="E130" s="1">
         <v>5520000</v>
       </c>
       <c r="F130" t="s">
@@ -4405,7 +4418,7 @@
       <c r="D131" t="s">
         <v>68</v>
       </c>
-      <c r="E131">
+      <c r="E131" s="1">
         <v>5290000</v>
       </c>
       <c r="F131" t="s">
@@ -4425,7 +4438,7 @@
       <c r="D132" t="s">
         <v>68</v>
       </c>
-      <c r="E132">
+      <c r="E132" s="1">
         <v>5290000</v>
       </c>
       <c r="F132" t="s">
@@ -4445,7 +4458,7 @@
       <c r="D133" t="s">
         <v>68</v>
       </c>
-      <c r="E133">
+      <c r="E133" s="1">
         <v>5290000</v>
       </c>
       <c r="F133" t="s">
@@ -4465,7 +4478,7 @@
       <c r="D134" t="s">
         <v>68</v>
       </c>
-      <c r="E134">
+      <c r="E134" s="1">
         <v>6210000</v>
       </c>
       <c r="F134" t="s">
@@ -4485,7 +4498,7 @@
       <c r="D135" t="s">
         <v>68</v>
       </c>
-      <c r="E135">
+      <c r="E135" s="1">
         <v>5290000</v>
       </c>
       <c r="F135" t="s">
@@ -4505,7 +4518,7 @@
       <c r="D136" t="s">
         <v>68</v>
       </c>
-      <c r="E136">
+      <c r="E136" s="1">
         <v>5290000</v>
       </c>
       <c r="F136" t="s">
@@ -4525,7 +4538,7 @@
       <c r="D137" t="s">
         <v>68</v>
       </c>
-      <c r="E137">
+      <c r="E137" s="1">
         <v>5290000</v>
       </c>
       <c r="F137" t="s">
@@ -4545,7 +4558,7 @@
       <c r="D138" t="s">
         <v>68</v>
       </c>
-      <c r="E138">
+      <c r="E138" s="1">
         <v>6210000</v>
       </c>
       <c r="F138" t="s">
@@ -4565,7 +4578,7 @@
       <c r="D139" t="s">
         <v>68</v>
       </c>
-      <c r="E139">
+      <c r="E139" s="1">
         <v>5290000</v>
       </c>
       <c r="F139" t="s">
@@ -4585,7 +4598,7 @@
       <c r="D140" t="s">
         <v>68</v>
       </c>
-      <c r="E140">
+      <c r="E140" s="1">
         <v>5290000</v>
       </c>
       <c r="F140" t="s">
@@ -4605,7 +4618,7 @@
       <c r="D141" t="s">
         <v>68</v>
       </c>
-      <c r="E141">
+      <c r="E141" s="1">
         <v>5290000</v>
       </c>
       <c r="F141" t="s">
@@ -4625,7 +4638,7 @@
       <c r="D142" t="s">
         <v>68</v>
       </c>
-      <c r="E142">
+      <c r="E142" s="1">
         <v>5520000</v>
       </c>
       <c r="F142" t="s">
@@ -4645,7 +4658,7 @@
       <c r="D143" t="s">
         <v>68</v>
       </c>
-      <c r="E143">
+      <c r="E143" s="1">
         <v>8165000</v>
       </c>
       <c r="F143" t="s">
@@ -4665,7 +4678,7 @@
       <c r="D144" t="s">
         <v>68</v>
       </c>
-      <c r="E144">
+      <c r="E144" s="1">
         <v>6555000</v>
       </c>
       <c r="F144" t="s">
@@ -4685,7 +4698,7 @@
       <c r="D145" t="s">
         <v>68</v>
       </c>
-      <c r="E145">
+      <c r="E145" s="1">
         <v>7015000</v>
       </c>
       <c r="F145" t="s">
@@ -4705,7 +4718,7 @@
       <c r="D146" t="s">
         <v>68</v>
       </c>
-      <c r="E146">
+      <c r="E146" s="1">
         <v>8250000</v>
       </c>
       <c r="F146" t="s">
@@ -4725,7 +4738,7 @@
       <c r="D147" t="s">
         <v>68</v>
       </c>
-      <c r="E147">
+      <c r="E147" s="1">
         <v>8250000</v>
       </c>
       <c r="F147" t="s">
@@ -4745,7 +4758,7 @@
       <c r="D148" t="s">
         <v>68</v>
       </c>
-      <c r="E148">
+      <c r="E148" s="1">
         <v>8250000</v>
       </c>
       <c r="F148" t="s">
@@ -4765,7 +4778,7 @@
       <c r="D149" t="s">
         <v>68</v>
       </c>
-      <c r="E149">
+      <c r="E149" s="1">
         <v>8250000</v>
       </c>
       <c r="F149" t="s">
@@ -4785,7 +4798,7 @@
       <c r="D150" t="s">
         <v>68</v>
       </c>
-      <c r="E150">
+      <c r="E150" s="1">
         <v>8165000</v>
       </c>
       <c r="F150" t="s">
@@ -4805,7 +4818,7 @@
       <c r="D151" t="s">
         <v>68</v>
       </c>
-      <c r="E151">
+      <c r="E151" s="1">
         <v>8250000</v>
       </c>
       <c r="F151" t="s">
@@ -4825,7 +4838,7 @@
       <c r="D152" t="s">
         <v>68</v>
       </c>
-      <c r="E152">
+      <c r="E152" s="1">
         <v>9500000</v>
       </c>
       <c r="F152" t="s">
@@ -4845,7 +4858,7 @@
       <c r="D153" t="s">
         <v>68</v>
       </c>
-      <c r="E153">
+      <c r="E153" s="1">
         <v>8250000</v>
       </c>
       <c r="F153" t="s">
@@ -4865,7 +4878,7 @@
       <c r="D154" t="s">
         <v>68</v>
       </c>
-      <c r="E154">
+      <c r="E154" s="1">
         <v>8250000</v>
       </c>
       <c r="F154" t="s">
@@ -4885,7 +4898,7 @@
       <c r="D155" t="s">
         <v>68</v>
       </c>
-      <c r="E155">
+      <c r="E155" s="1">
         <v>6325000</v>
       </c>
       <c r="F155" t="s">
@@ -4905,7 +4918,7 @@
       <c r="D156" t="s">
         <v>68</v>
       </c>
-      <c r="E156">
+      <c r="E156" s="1">
         <v>6555000</v>
       </c>
       <c r="F156" t="s">
@@ -4925,7 +4938,7 @@
       <c r="D157" t="s">
         <v>68</v>
       </c>
-      <c r="E157">
+      <c r="E157" s="1">
         <v>6325000</v>
       </c>
       <c r="F157" t="s">
@@ -4945,7 +4958,7 @@
       <c r="D158" t="s">
         <v>68</v>
       </c>
-      <c r="E158">
+      <c r="E158" s="1">
         <v>6785000</v>
       </c>
       <c r="F158" t="s">
@@ -4965,7 +4978,7 @@
       <c r="D159" t="s">
         <v>68</v>
       </c>
-      <c r="E159">
+      <c r="E159" s="1">
         <v>6785000</v>
       </c>
       <c r="F159" t="s">
@@ -4985,7 +4998,7 @@
       <c r="D160" t="s">
         <v>68</v>
       </c>
-      <c r="E160">
+      <c r="E160" s="1">
         <v>6325000</v>
       </c>
       <c r="F160" t="s">
@@ -5005,7 +5018,7 @@
       <c r="D161" t="s">
         <v>68</v>
       </c>
-      <c r="E161">
+      <c r="E161" s="1">
         <v>6555000</v>
       </c>
       <c r="F161" t="s">
@@ -5025,7 +5038,7 @@
       <c r="D162" t="s">
         <v>68</v>
       </c>
-      <c r="E162">
+      <c r="E162" s="1">
         <v>7245000</v>
       </c>
       <c r="F162" t="s">
@@ -5045,7 +5058,7 @@
       <c r="D163" t="s">
         <v>68</v>
       </c>
-      <c r="E163">
+      <c r="E163" s="1">
         <v>7245000</v>
       </c>
       <c r="F163" t="s">
@@ -5065,7 +5078,7 @@
       <c r="D164" t="s">
         <v>68</v>
       </c>
-      <c r="E164">
+      <c r="E164" s="1">
         <v>7245000</v>
       </c>
       <c r="F164" t="s">
@@ -5085,7 +5098,7 @@
       <c r="D165" t="s">
         <v>68</v>
       </c>
-      <c r="E165">
+      <c r="E165" s="1">
         <v>6785000</v>
       </c>
       <c r="F165" t="s">
@@ -5105,7 +5118,7 @@
       <c r="D166" t="s">
         <v>68</v>
       </c>
-      <c r="E166">
+      <c r="E166" s="1">
         <v>7705000</v>
       </c>
       <c r="F166" t="s">
@@ -5125,7 +5138,7 @@
       <c r="D167" t="s">
         <v>68</v>
       </c>
-      <c r="E167">
+      <c r="E167" s="1">
         <v>6325000</v>
       </c>
       <c r="F167" t="s">
@@ -5145,7 +5158,7 @@
       <c r="D168" t="s">
         <v>68</v>
       </c>
-      <c r="E168">
+      <c r="E168" s="1">
         <v>6325000</v>
       </c>
       <c r="F168" t="s">
@@ -5165,7 +5178,7 @@
       <c r="D169" t="s">
         <v>68</v>
       </c>
-      <c r="E169">
+      <c r="E169" s="1">
         <v>6555000</v>
       </c>
       <c r="F169" t="s">
@@ -5185,7 +5198,7 @@
       <c r="D170" t="s">
         <v>68</v>
       </c>
-      <c r="E170">
+      <c r="E170" s="1">
         <v>6325000</v>
       </c>
       <c r="F170" t="s">
@@ -5205,7 +5218,7 @@
       <c r="D171" t="s">
         <v>68</v>
       </c>
-      <c r="E171">
+      <c r="E171" s="1">
         <v>6555000</v>
       </c>
       <c r="F171" t="s">
@@ -5225,7 +5238,7 @@
       <c r="D172" t="s">
         <v>68</v>
       </c>
-      <c r="E172">
+      <c r="E172" s="1">
         <v>7705000</v>
       </c>
       <c r="F172" t="s">
@@ -5245,7 +5258,7 @@
       <c r="D173" t="s">
         <v>68</v>
       </c>
-      <c r="E173">
+      <c r="E173" s="1">
         <v>6785000</v>
       </c>
       <c r="F173" t="s">
@@ -5265,7 +5278,7 @@
       <c r="D174" t="s">
         <v>68</v>
       </c>
-      <c r="E174">
+      <c r="E174" s="1">
         <v>6785000</v>
       </c>
       <c r="F174" t="s">
@@ -5285,7 +5298,7 @@
       <c r="D175" t="s">
         <v>68</v>
       </c>
-      <c r="E175">
+      <c r="E175" s="1">
         <v>6785000</v>
       </c>
       <c r="F175" t="s">
@@ -5305,7 +5318,7 @@
       <c r="D176" t="s">
         <v>68</v>
       </c>
-      <c r="E176">
+      <c r="E176" s="1">
         <v>7705000</v>
       </c>
       <c r="F176" t="s">
@@ -5325,7 +5338,7 @@
       <c r="D177" t="s">
         <v>68</v>
       </c>
-      <c r="E177">
+      <c r="E177" s="1">
         <v>6555000</v>
       </c>
       <c r="F177" t="s">
@@ -5345,7 +5358,7 @@
       <c r="D178" t="s">
         <v>68</v>
       </c>
-      <c r="E178">
+      <c r="E178" s="1">
         <v>6555000</v>
       </c>
       <c r="F178" t="s">
@@ -5365,7 +5378,7 @@
       <c r="D179" t="s">
         <v>68</v>
       </c>
-      <c r="E179">
+      <c r="E179" s="1">
         <v>6555000</v>
       </c>
       <c r="F179" t="s">
@@ -5385,7 +5398,7 @@
       <c r="D180" t="s">
         <v>68</v>
       </c>
-      <c r="E180">
+      <c r="E180" s="1">
         <v>6555000</v>
       </c>
       <c r="F180" t="s">
@@ -5405,7 +5418,7 @@
       <c r="D181" t="s">
         <v>68</v>
       </c>
-      <c r="E181">
+      <c r="E181" s="1">
         <v>6555000</v>
       </c>
       <c r="F181" t="s">
@@ -5425,7 +5438,7 @@
       <c r="D182" t="s">
         <v>68</v>
       </c>
-      <c r="E182">
+      <c r="E182" s="1">
         <v>6555000</v>
       </c>
       <c r="F182" t="s">
@@ -5445,7 +5458,7 @@
       <c r="D183" t="s">
         <v>68</v>
       </c>
-      <c r="E183">
+      <c r="E183" s="1">
         <v>6555000</v>
       </c>
       <c r="F183" t="s">
@@ -5465,7 +5478,7 @@
       <c r="D184" t="s">
         <v>68</v>
       </c>
-      <c r="E184">
+      <c r="E184" s="1">
         <v>6785000</v>
       </c>
       <c r="F184" t="s">
@@ -5485,7 +5498,7 @@
       <c r="D185" t="s">
         <v>68</v>
       </c>
-      <c r="E185">
+      <c r="E185" s="1">
         <v>7705000</v>
       </c>
       <c r="F185" t="s">
@@ -5505,7 +5518,7 @@
       <c r="D186" t="s">
         <v>68</v>
       </c>
-      <c r="E186">
+      <c r="E186" s="1">
         <v>6325000</v>
       </c>
       <c r="F186" t="s">
@@ -5525,7 +5538,7 @@
       <c r="D187" t="s">
         <v>68</v>
       </c>
-      <c r="E187">
+      <c r="E187" s="1">
         <v>6325000</v>
       </c>
       <c r="F187" t="s">
@@ -5545,7 +5558,7 @@
       <c r="D188" t="s">
         <v>68</v>
       </c>
-      <c r="E188">
+      <c r="E188" s="1">
         <v>6555000</v>
       </c>
       <c r="F188" t="s">
@@ -5565,7 +5578,7 @@
       <c r="D189" t="s">
         <v>68</v>
       </c>
-      <c r="E189">
+      <c r="E189" s="1">
         <v>7015000</v>
       </c>
       <c r="F189" t="s">
@@ -5585,7 +5598,7 @@
       <c r="D190" t="s">
         <v>68</v>
       </c>
-      <c r="E190">
+      <c r="E190" s="1">
         <v>6555000</v>
       </c>
       <c r="F190" t="s">
@@ -5605,7 +5618,7 @@
       <c r="D191" t="s">
         <v>68</v>
       </c>
-      <c r="E191">
+      <c r="E191" s="1">
         <v>6555000</v>
       </c>
       <c r="F191" t="s">
@@ -5625,7 +5638,7 @@
       <c r="D192" t="s">
         <v>68</v>
       </c>
-      <c r="E192">
+      <c r="E192" s="1">
         <v>6555000</v>
       </c>
       <c r="F192" t="s">
@@ -5645,7 +5658,7 @@
       <c r="D193" t="s">
         <v>68</v>
       </c>
-      <c r="E193">
+      <c r="E193" s="1">
         <v>6785000</v>
       </c>
       <c r="F193" t="s">
@@ -5665,7 +5678,7 @@
       <c r="D194" t="s">
         <v>68</v>
       </c>
-      <c r="E194">
+      <c r="E194" s="1">
         <v>6555000</v>
       </c>
       <c r="F194" t="s">
@@ -5685,7 +5698,7 @@
       <c r="D195" t="s">
         <v>68</v>
       </c>
-      <c r="E195">
+      <c r="E195" s="1">
         <v>6555000</v>
       </c>
       <c r="F195" t="s">
@@ -5705,7 +5718,7 @@
       <c r="D196" t="s">
         <v>68</v>
       </c>
-      <c r="E196">
+      <c r="E196" s="1">
         <v>6785000</v>
       </c>
       <c r="F196" t="s">
@@ -5725,7 +5738,7 @@
       <c r="D197" t="s">
         <v>68</v>
       </c>
-      <c r="E197">
+      <c r="E197" s="1">
         <v>6555000</v>
       </c>
       <c r="F197" t="s">
@@ -5745,7 +5758,7 @@
       <c r="D198" t="s">
         <v>68</v>
       </c>
-      <c r="E198">
+      <c r="E198" s="1">
         <v>6555000</v>
       </c>
       <c r="F198" t="s">
@@ -5765,7 +5778,7 @@
       <c r="D199" t="s">
         <v>68</v>
       </c>
-      <c r="E199">
+      <c r="E199" s="1">
         <v>6325000</v>
       </c>
       <c r="F199" t="s">
@@ -5785,7 +5798,7 @@
       <c r="D200" t="s">
         <v>68</v>
       </c>
-      <c r="E200">
+      <c r="E200" s="1">
         <v>7245000</v>
       </c>
       <c r="F200" t="s">
@@ -5805,7 +5818,7 @@
       <c r="D201" t="s">
         <v>68</v>
       </c>
-      <c r="E201">
+      <c r="E201" s="1">
         <v>6555000</v>
       </c>
       <c r="F201" t="s">
@@ -5825,7 +5838,7 @@
       <c r="D202" t="s">
         <v>68</v>
       </c>
-      <c r="E202">
+      <c r="E202" s="1">
         <v>6555000</v>
       </c>
       <c r="F202" t="s">
@@ -5845,7 +5858,7 @@
       <c r="D203" t="s">
         <v>68</v>
       </c>
-      <c r="E203">
+      <c r="E203" s="1">
         <v>6555000</v>
       </c>
       <c r="F203" t="s">
@@ -5865,7 +5878,7 @@
       <c r="D204" t="s">
         <v>68</v>
       </c>
-      <c r="E204">
+      <c r="E204" s="1">
         <v>6555000</v>
       </c>
       <c r="F204" t="s">
@@ -5885,7 +5898,7 @@
       <c r="D205" t="s">
         <v>68</v>
       </c>
-      <c r="E205">
+      <c r="E205" s="1">
         <v>7015000</v>
       </c>
       <c r="F205" t="s">
@@ -5905,7 +5918,7 @@
       <c r="D206" t="s">
         <v>68</v>
       </c>
-      <c r="E206">
+      <c r="E206" s="1">
         <v>7935000</v>
       </c>
       <c r="F206" t="s">
@@ -5925,7 +5938,7 @@
       <c r="D207" t="s">
         <v>68</v>
       </c>
-      <c r="E207">
+      <c r="E207" s="1">
         <v>6785000</v>
       </c>
       <c r="F207" t="s">
@@ -5945,7 +5958,7 @@
       <c r="D208" t="s">
         <v>68</v>
       </c>
-      <c r="E208">
+      <c r="E208" s="1">
         <v>6555000</v>
       </c>
       <c r="F208" t="s">
@@ -5965,7 +5978,7 @@
       <c r="D209" t="s">
         <v>68</v>
       </c>
-      <c r="E209">
+      <c r="E209" s="1">
         <v>6555000</v>
       </c>
       <c r="F209" t="s">
@@ -5985,7 +5998,7 @@
       <c r="D210" t="s">
         <v>68</v>
       </c>
-      <c r="E210">
+      <c r="E210" s="1">
         <v>6555000</v>
       </c>
       <c r="F210" t="s">
@@ -6005,7 +6018,7 @@
       <c r="D211" t="s">
         <v>68</v>
       </c>
-      <c r="E211">
+      <c r="E211" s="1">
         <v>7475000</v>
       </c>
       <c r="F211" t="s">
@@ -6025,7 +6038,7 @@
       <c r="D212" t="s">
         <v>68</v>
       </c>
-      <c r="E212">
+      <c r="E212" s="1">
         <v>6555000</v>
       </c>
       <c r="F212" t="s">
@@ -6045,7 +6058,7 @@
       <c r="D213" t="s">
         <v>68</v>
       </c>
-      <c r="E213">
+      <c r="E213" s="1">
         <v>6555000</v>
       </c>
       <c r="F213" t="s">
@@ -6065,7 +6078,7 @@
       <c r="D214" t="s">
         <v>68</v>
       </c>
-      <c r="E214">
+      <c r="E214" s="1">
         <v>6555000</v>
       </c>
       <c r="F214" t="s">
@@ -6085,7 +6098,7 @@
       <c r="D215" t="s">
         <v>68</v>
       </c>
-      <c r="E215">
+      <c r="E215" s="1">
         <v>7475000</v>
       </c>
       <c r="F215" t="s">
@@ -6105,7 +6118,7 @@
       <c r="D216" t="s">
         <v>68</v>
       </c>
-      <c r="E216">
+      <c r="E216" s="1">
         <v>6555000</v>
       </c>
       <c r="F216" t="s">
@@ -6125,7 +6138,7 @@
       <c r="D217" t="s">
         <v>68</v>
       </c>
-      <c r="E217">
+      <c r="E217" s="1">
         <v>6555000</v>
       </c>
       <c r="F217" t="s">
@@ -6145,7 +6158,7 @@
       <c r="D218" t="s">
         <v>68</v>
       </c>
-      <c r="E218">
+      <c r="E218" s="1">
         <v>6555000</v>
       </c>
       <c r="F218" t="s">
@@ -6165,7 +6178,7 @@
       <c r="D219" t="s">
         <v>68</v>
       </c>
-      <c r="E219">
+      <c r="E219" s="1">
         <v>6785000</v>
       </c>
       <c r="F219" t="s">
@@ -6185,7 +6198,7 @@
       <c r="D220" t="s">
         <v>238</v>
       </c>
-      <c r="E220">
+      <c r="E220" s="1">
         <v>350000</v>
       </c>
       <c r="F220" t="s">
@@ -6205,7 +6218,7 @@
       <c r="D221" t="s">
         <v>238</v>
       </c>
-      <c r="E221">
+      <c r="E221" s="1">
         <v>350000</v>
       </c>
       <c r="F221" t="s">
@@ -6225,7 +6238,7 @@
       <c r="D222" t="s">
         <v>238</v>
       </c>
-      <c r="E222">
+      <c r="E222" s="1">
         <v>300000</v>
       </c>
       <c r="F222" t="s">
@@ -6245,7 +6258,7 @@
       <c r="D223" t="s">
         <v>17</v>
       </c>
-      <c r="E223">
+      <c r="E223" s="1">
         <v>1500000</v>
       </c>
       <c r="F223" t="s">
@@ -6265,7 +6278,7 @@
       <c r="D224" t="s">
         <v>238</v>
       </c>
-      <c r="E224">
+      <c r="E224" s="1">
         <v>300000</v>
       </c>
       <c r="F224" t="s">
@@ -6285,7 +6298,7 @@
       <c r="D225" t="s">
         <v>238</v>
       </c>
-      <c r="E225">
+      <c r="E225" s="1">
         <v>300000</v>
       </c>
       <c r="F225" t="s">
@@ -6305,7 +6318,7 @@
       <c r="D226" t="s">
         <v>238</v>
       </c>
-      <c r="E226">
+      <c r="E226" s="1">
         <v>200000</v>
       </c>
       <c r="F226" t="s">
@@ -6325,7 +6338,7 @@
       <c r="D227" t="s">
         <v>17</v>
       </c>
-      <c r="E227">
+      <c r="E227" s="1">
         <v>1500000</v>
       </c>
       <c r="F227" t="s">
@@ -6345,7 +6358,7 @@
       <c r="D228" t="s">
         <v>17</v>
       </c>
-      <c r="E228">
+      <c r="E228" s="1">
         <v>1500000</v>
       </c>
       <c r="F228" t="s">
@@ -6365,7 +6378,7 @@
       <c r="D229" t="s">
         <v>68</v>
       </c>
-      <c r="E229">
+      <c r="E229" s="1">
         <v>12500000</v>
       </c>
       <c r="F229" t="s">
@@ -6385,7 +6398,7 @@
       <c r="D230" t="s">
         <v>68</v>
       </c>
-      <c r="E230">
+      <c r="E230" s="1">
         <v>12500000</v>
       </c>
       <c r="F230" t="s">
@@ -6405,7 +6418,7 @@
       <c r="D231" t="s">
         <v>68</v>
       </c>
-      <c r="E231">
+      <c r="E231" s="1">
         <v>7500000</v>
       </c>
       <c r="F231" t="s">
@@ -6425,7 +6438,7 @@
       <c r="D232" t="s">
         <v>68</v>
       </c>
-      <c r="E232">
+      <c r="E232" s="1">
         <v>7500000</v>
       </c>
       <c r="F232" t="s">
@@ -6445,7 +6458,7 @@
       <c r="D233" t="s">
         <v>17</v>
       </c>
-      <c r="E233">
+      <c r="E233" s="1">
         <v>8500000</v>
       </c>
       <c r="F233" t="s">
@@ -6465,7 +6478,7 @@
       <c r="D234" t="s">
         <v>17</v>
       </c>
-      <c r="E234">
+      <c r="E234" s="1">
         <v>8000000</v>
       </c>
       <c r="F234" t="s">
@@ -6485,7 +6498,7 @@
       <c r="D235" t="s">
         <v>17</v>
       </c>
-      <c r="E235">
+      <c r="E235" s="1">
         <v>3500000</v>
       </c>
       <c r="F235" t="s">
@@ -6505,7 +6518,7 @@
       <c r="D236" t="s">
         <v>17</v>
       </c>
-      <c r="E236">
+      <c r="E236" s="1">
         <v>3000000</v>
       </c>
       <c r="F236" t="s">
@@ -6525,7 +6538,7 @@
       <c r="D237" t="s">
         <v>17</v>
       </c>
-      <c r="E237">
+      <c r="E237" s="1">
         <v>3000000</v>
       </c>
       <c r="F237" t="s">
@@ -6545,7 +6558,7 @@
       <c r="D238" t="s">
         <v>17</v>
       </c>
-      <c r="E238">
+      <c r="E238" s="1">
         <v>2500000</v>
       </c>
       <c r="F238" t="s">
@@ -6565,7 +6578,7 @@
       <c r="D239" t="s">
         <v>17</v>
       </c>
-      <c r="E239">
+      <c r="E239" s="1">
         <v>3000000</v>
       </c>
       <c r="F239" t="s">
@@ -6585,7 +6598,7 @@
       <c r="D240" t="s">
         <v>17</v>
       </c>
-      <c r="E240">
+      <c r="E240" s="1">
         <v>3500000</v>
       </c>
       <c r="F240" t="s">
@@ -6605,7 +6618,7 @@
       <c r="D241" t="s">
         <v>17</v>
       </c>
-      <c r="E241">
+      <c r="E241" s="1">
         <v>2750000</v>
       </c>
       <c r="F241" t="s">
@@ -6625,7 +6638,7 @@
       <c r="D242" t="s">
         <v>17</v>
       </c>
-      <c r="E242">
+      <c r="E242" s="1">
         <v>4000000</v>
       </c>
       <c r="F242" t="s">
@@ -6645,7 +6658,7 @@
       <c r="D243" t="s">
         <v>17</v>
       </c>
-      <c r="E243">
+      <c r="E243" s="1">
         <v>2250000</v>
       </c>
       <c r="F243" t="s">
@@ -6665,7 +6678,7 @@
       <c r="D244" t="s">
         <v>17</v>
       </c>
-      <c r="E244">
+      <c r="E244" s="1">
         <v>5000000</v>
       </c>
       <c r="F244" t="s">
@@ -6685,7 +6698,7 @@
       <c r="D245" t="s">
         <v>9</v>
       </c>
-      <c r="E245">
+      <c r="E245" s="1">
         <v>50000000</v>
       </c>
       <c r="F245" t="s">
@@ -6705,7 +6718,7 @@
       <c r="D246" t="s">
         <v>9</v>
       </c>
-      <c r="E246">
+      <c r="E246" s="1">
         <v>60000000</v>
       </c>
       <c r="F246" t="s">
@@ -6725,7 +6738,7 @@
       <c r="D247" t="s">
         <v>9</v>
       </c>
-      <c r="E247">
+      <c r="E247" s="1">
         <v>40000000</v>
       </c>
       <c r="F247" t="s">
@@ -6745,7 +6758,7 @@
       <c r="D248" t="s">
         <v>9</v>
       </c>
-      <c r="E248">
+      <c r="E248" s="1">
         <v>15000000</v>
       </c>
       <c r="F248" t="s">
@@ -6765,7 +6778,7 @@
       <c r="D249" t="s">
         <v>9</v>
       </c>
-      <c r="E249">
+      <c r="E249" s="1">
         <v>25000000</v>
       </c>
       <c r="F249" t="s">
@@ -6785,7 +6798,7 @@
       <c r="D250" t="s">
         <v>68</v>
       </c>
-      <c r="E250">
+      <c r="E250" s="1">
         <v>7500000</v>
       </c>
       <c r="F250" t="s">
@@ -6805,7 +6818,7 @@
       <c r="D251" t="s">
         <v>17</v>
       </c>
-      <c r="E251">
+      <c r="E251" s="1">
         <v>750000</v>
       </c>
       <c r="F251" t="s">
@@ -6825,7 +6838,7 @@
       <c r="D252" t="s">
         <v>271</v>
       </c>
-      <c r="E252">
+      <c r="E252" s="1">
         <v>25000</v>
       </c>
       <c r="F252" t="s">
@@ -6845,7 +6858,7 @@
       <c r="D253" t="s">
         <v>40</v>
       </c>
-      <c r="E253">
+      <c r="E253" s="1">
         <v>1500000</v>
       </c>
       <c r="F253" t="s">
@@ -6865,7 +6878,7 @@
       <c r="D254" t="s">
         <v>40</v>
       </c>
-      <c r="E254">
+      <c r="E254" s="1">
         <v>1200000</v>
       </c>
       <c r="F254" t="s">
@@ -6885,7 +6898,7 @@
       <c r="D255" t="s">
         <v>40</v>
       </c>
-      <c r="E255">
+      <c r="E255" s="1">
         <v>344500</v>
       </c>
       <c r="F255" t="s">
@@ -6905,7 +6918,7 @@
       <c r="D256" t="s">
         <v>40</v>
       </c>
-      <c r="E256">
+      <c r="E256" s="1">
         <v>344500</v>
       </c>
       <c r="F256" t="s">
@@ -6925,7 +6938,7 @@
       <c r="D257" t="s">
         <v>40</v>
       </c>
-      <c r="E257">
+      <c r="E257" s="1">
         <v>150000</v>
       </c>
       <c r="F257" t="s">
@@ -6945,7 +6958,7 @@
       <c r="D258" t="s">
         <v>40</v>
       </c>
-      <c r="E258">
+      <c r="E258" s="1">
         <v>195000</v>
       </c>
       <c r="F258" t="s">
@@ -6965,7 +6978,7 @@
       <c r="D259" t="s">
         <v>77</v>
       </c>
-      <c r="E259">
+      <c r="E259" s="1">
         <v>37500</v>
       </c>
       <c r="F259" t="s">
@@ -6985,7 +6998,7 @@
       <c r="D260" t="s">
         <v>40</v>
       </c>
-      <c r="E260">
+      <c r="E260" s="1">
         <v>312000</v>
       </c>
       <c r="F260" t="s">
@@ -7005,7 +7018,7 @@
       <c r="D261" t="s">
         <v>40</v>
       </c>
-      <c r="E261">
+      <c r="E261" s="1">
         <v>250000</v>
       </c>
       <c r="F261" t="s">
@@ -7025,7 +7038,7 @@
       <c r="D262" t="s">
         <v>40</v>
       </c>
-      <c r="E262">
+      <c r="E262" s="1">
         <v>250000</v>
       </c>
       <c r="F262" t="s">
@@ -7045,7 +7058,7 @@
       <c r="D263" t="s">
         <v>40</v>
       </c>
-      <c r="E263">
+      <c r="E263" s="1">
         <v>450000</v>
       </c>
       <c r="F263" t="s">
@@ -7065,7 +7078,7 @@
       <c r="D264" t="s">
         <v>40</v>
       </c>
-      <c r="E264">
+      <c r="E264" s="1">
         <v>400000</v>
       </c>
       <c r="F264" t="s">
@@ -7085,7 +7098,7 @@
       <c r="D265" t="s">
         <v>71</v>
       </c>
-      <c r="E265">
+      <c r="E265" s="1">
         <v>4375000</v>
       </c>
       <c r="F265" t="s">
@@ -7105,7 +7118,7 @@
       <c r="D266" t="s">
         <v>71</v>
       </c>
-      <c r="E266">
+      <c r="E266" s="1">
         <v>4375000</v>
       </c>
       <c r="F266" t="s">
@@ -7125,7 +7138,7 @@
       <c r="D267" t="s">
         <v>71</v>
       </c>
-      <c r="E267">
+      <c r="E267" s="1">
         <v>3125000</v>
       </c>
       <c r="F267" t="s">
@@ -7145,7 +7158,7 @@
       <c r="D268" t="s">
         <v>71</v>
       </c>
-      <c r="E268">
+      <c r="E268" s="1">
         <v>3125000</v>
       </c>
       <c r="F268" t="s">
@@ -7165,7 +7178,7 @@
       <c r="D269" t="s">
         <v>71</v>
       </c>
-      <c r="E269">
+      <c r="E269" s="1">
         <v>4375000</v>
       </c>
       <c r="F269" t="s">
@@ -7185,7 +7198,7 @@
       <c r="D270" t="s">
         <v>71</v>
       </c>
-      <c r="E270">
+      <c r="E270" s="1">
         <v>4375000</v>
       </c>
       <c r="F270" t="s">
@@ -7205,7 +7218,7 @@
       <c r="D271" t="s">
         <v>71</v>
       </c>
-      <c r="E271">
+      <c r="E271" s="1">
         <v>4375000</v>
       </c>
       <c r="F271" t="s">
@@ -7225,7 +7238,7 @@
       <c r="D272" t="s">
         <v>71</v>
       </c>
-      <c r="E272">
+      <c r="E272" s="1">
         <v>3125000</v>
       </c>
       <c r="F272" t="s">
@@ -7245,7 +7258,7 @@
       <c r="D273" t="s">
         <v>71</v>
       </c>
-      <c r="E273">
+      <c r="E273" s="1">
         <v>3125000</v>
       </c>
       <c r="F273" t="s">
@@ -7265,7 +7278,7 @@
       <c r="D274" t="s">
         <v>71</v>
       </c>
-      <c r="E274">
+      <c r="E274" s="1">
         <v>3125000</v>
       </c>
       <c r="F274" t="s">
@@ -7285,7 +7298,7 @@
       <c r="D275" t="s">
         <v>71</v>
       </c>
-      <c r="E275">
+      <c r="E275" s="1">
         <v>4375000</v>
       </c>
       <c r="F275" t="s">
@@ -7305,7 +7318,7 @@
       <c r="D276" t="s">
         <v>71</v>
       </c>
-      <c r="E276">
+      <c r="E276" s="1">
         <v>4375000</v>
       </c>
       <c r="F276" t="s">
@@ -7325,7 +7338,7 @@
       <c r="D277" t="s">
         <v>71</v>
       </c>
-      <c r="E277">
+      <c r="E277" s="1">
         <v>3125000</v>
       </c>
       <c r="F277" t="s">
@@ -7345,7 +7358,7 @@
       <c r="D278" t="s">
         <v>71</v>
       </c>
-      <c r="E278">
+      <c r="E278" s="1">
         <v>3125000</v>
       </c>
       <c r="F278" t="s">
@@ -7365,7 +7378,7 @@
       <c r="D279" t="s">
         <v>40</v>
       </c>
-      <c r="E279">
+      <c r="E279" s="1">
         <v>19500</v>
       </c>
       <c r="F279" t="s">
@@ -7385,7 +7398,7 @@
       <c r="D280" t="s">
         <v>40</v>
       </c>
-      <c r="E280">
+      <c r="E280" s="1">
         <v>26250</v>
       </c>
       <c r="F280" t="s">
@@ -7405,7 +7418,7 @@
       <c r="D281" t="s">
         <v>40</v>
       </c>
-      <c r="E281">
+      <c r="E281" s="1">
         <v>562500</v>
       </c>
       <c r="F281" t="s">
@@ -7425,7 +7438,7 @@
       <c r="D282" t="s">
         <v>40</v>
       </c>
-      <c r="E282">
+      <c r="E282" s="1">
         <v>812000</v>
       </c>
       <c r="F282" t="s">
@@ -7445,7 +7458,7 @@
       <c r="D283" t="s">
         <v>77</v>
       </c>
-      <c r="E283">
+      <c r="E283" s="1">
         <v>312500</v>
       </c>
       <c r="F283" t="s">
@@ -7465,7 +7478,7 @@
       <c r="D284" t="s">
         <v>40</v>
       </c>
-      <c r="E284">
+      <c r="E284" s="1">
         <v>243750</v>
       </c>
       <c r="F284" t="s">
@@ -7485,7 +7498,7 @@
       <c r="D285" t="s">
         <v>40</v>
       </c>
-      <c r="E285">
+      <c r="E285" s="1">
         <v>55500</v>
       </c>
       <c r="F285" t="s">
@@ -7505,7 +7518,7 @@
       <c r="D286" t="s">
         <v>40</v>
       </c>
-      <c r="E286">
+      <c r="E286" s="1">
         <v>72000</v>
       </c>
       <c r="F286" t="s">
@@ -7525,7 +7538,7 @@
       <c r="D287" t="s">
         <v>40</v>
       </c>
-      <c r="E287">
+      <c r="E287" s="1">
         <v>75000</v>
       </c>
       <c r="F287" t="s">
@@ -7545,7 +7558,7 @@
       <c r="D288" t="s">
         <v>40</v>
       </c>
-      <c r="E288">
+      <c r="E288" s="1">
         <v>500000</v>
       </c>
       <c r="F288" t="s">
@@ -7565,7 +7578,7 @@
       <c r="D289" t="s">
         <v>40</v>
       </c>
-      <c r="E289">
+      <c r="E289" s="1">
         <v>950000</v>
       </c>
       <c r="F289" t="s">
@@ -7585,7 +7598,7 @@
       <c r="D290" t="s">
         <v>40</v>
       </c>
-      <c r="E290">
+      <c r="E290" s="1">
         <v>250000</v>
       </c>
       <c r="F290" t="s">
@@ -7605,7 +7618,7 @@
       <c r="D291" t="s">
         <v>40</v>
       </c>
-      <c r="E291">
+      <c r="E291" s="1">
         <v>122500</v>
       </c>
       <c r="F291" t="s">
@@ -7625,7 +7638,7 @@
       <c r="D292" t="s">
         <v>40</v>
       </c>
-      <c r="E292">
+      <c r="E292" s="1">
         <v>22500</v>
       </c>
       <c r="F292" t="s">
@@ -7645,7 +7658,7 @@
       <c r="D293" t="s">
         <v>40</v>
       </c>
-      <c r="E293">
+      <c r="E293" s="1">
         <v>4500</v>
       </c>
       <c r="F293" t="s">
@@ -7665,7 +7678,7 @@
       <c r="D294" t="s">
         <v>40</v>
       </c>
-      <c r="E294">
+      <c r="E294" s="1">
         <v>6000</v>
       </c>
       <c r="F294" t="s">
@@ -7685,7 +7698,7 @@
       <c r="D295" t="s">
         <v>40</v>
       </c>
-      <c r="E295">
+      <c r="E295" s="1">
         <v>7500</v>
       </c>
       <c r="F295" t="s">
@@ -7705,7 +7718,7 @@
       <c r="D296" t="s">
         <v>40</v>
       </c>
-      <c r="E296">
+      <c r="E296" s="1">
         <v>73125</v>
       </c>
       <c r="F296" t="s">
@@ -7725,7 +7738,7 @@
       <c r="D297" t="s">
         <v>40</v>
       </c>
-      <c r="E297">
+      <c r="E297" s="1">
         <v>62500</v>
       </c>
       <c r="F297" t="s">
@@ -7745,7 +7758,7 @@
       <c r="D298" t="s">
         <v>40</v>
       </c>
-      <c r="E298">
+      <c r="E298" s="1">
         <v>22500</v>
       </c>
       <c r="F298" t="s">
@@ -7765,7 +7778,7 @@
       <c r="D299" t="s">
         <v>40</v>
       </c>
-      <c r="E299">
+      <c r="E299" s="1">
         <v>12000</v>
       </c>
       <c r="F299" t="s">
@@ -7785,7 +7798,7 @@
       <c r="D300" t="s">
         <v>40</v>
       </c>
-      <c r="E300">
+      <c r="E300" s="1">
         <v>62500</v>
       </c>
       <c r="F300" t="s">
@@ -7805,7 +7818,7 @@
       <c r="D301" t="s">
         <v>40</v>
       </c>
-      <c r="E301">
+      <c r="E301" s="1">
         <v>6000</v>
       </c>
       <c r="F301" t="s">
@@ -7825,7 +7838,7 @@
       <c r="D302" t="s">
         <v>40</v>
       </c>
-      <c r="E302">
+      <c r="E302" s="1">
         <v>37500</v>
       </c>
       <c r="F302" t="s">
@@ -7845,7 +7858,7 @@
       <c r="D303" t="s">
         <v>40</v>
       </c>
-      <c r="E303">
+      <c r="E303" s="1">
         <v>10000</v>
       </c>
       <c r="F303" t="s">
@@ -7865,7 +7878,7 @@
       <c r="D304" t="s">
         <v>40</v>
       </c>
-      <c r="E304">
+      <c r="E304" s="1">
         <v>93750</v>
       </c>
       <c r="F304" t="s">
@@ -7885,7 +7898,7 @@
       <c r="D305" t="s">
         <v>40</v>
       </c>
-      <c r="E305">
+      <c r="E305" s="1">
         <v>112500</v>
       </c>
       <c r="F305" t="s">
@@ -7905,7 +7918,7 @@
       <c r="D306" t="s">
         <v>40</v>
       </c>
-      <c r="E306">
+      <c r="E306" s="1">
         <v>21250</v>
       </c>
       <c r="F306" t="s">
@@ -7925,7 +7938,7 @@
       <c r="D307" t="s">
         <v>40</v>
       </c>
-      <c r="E307">
+      <c r="E307" s="1">
         <v>12500</v>
       </c>
       <c r="F307" t="s">
@@ -7945,7 +7958,7 @@
       <c r="D308" t="s">
         <v>40</v>
       </c>
-      <c r="E308">
+      <c r="E308" s="1">
         <v>75000</v>
       </c>
       <c r="F308" t="s">
@@ -7965,7 +7978,7 @@
       <c r="D309" t="s">
         <v>40</v>
       </c>
-      <c r="E309">
+      <c r="E309" s="1">
         <v>10000</v>
       </c>
       <c r="F309" t="s">
@@ -7985,7 +7998,7 @@
       <c r="D310" t="s">
         <v>40</v>
       </c>
-      <c r="E310">
+      <c r="E310" s="1">
         <v>13000</v>
       </c>
       <c r="F310" t="s">
@@ -8005,7 +8018,7 @@
       <c r="D311" t="s">
         <v>40</v>
       </c>
-      <c r="E311">
+      <c r="E311" s="1">
         <v>10000</v>
       </c>
       <c r="F311" t="s">
@@ -8025,7 +8038,7 @@
       <c r="D312" t="s">
         <v>40</v>
       </c>
-      <c r="E312">
+      <c r="E312" s="1">
         <v>12000</v>
       </c>
       <c r="F312" t="s">
@@ -8045,7 +8058,7 @@
       <c r="D313" t="s">
         <v>40</v>
       </c>
-      <c r="E313">
+      <c r="E313" s="1">
         <v>28750</v>
       </c>
       <c r="F313" t="s">
@@ -8065,7 +8078,7 @@
       <c r="D314" t="s">
         <v>40</v>
       </c>
-      <c r="E314">
+      <c r="E314" s="1">
         <v>28750</v>
       </c>
       <c r="F314" t="s">
@@ -8085,7 +8098,7 @@
       <c r="D315" t="s">
         <v>40</v>
       </c>
-      <c r="E315">
+      <c r="E315" s="1">
         <v>10000</v>
       </c>
       <c r="F315" t="s">
@@ -8105,7 +8118,7 @@
       <c r="D316" t="s">
         <v>40</v>
       </c>
-      <c r="E316">
+      <c r="E316" s="1">
         <v>50000</v>
       </c>
       <c r="F316" t="s">
@@ -8125,7 +8138,7 @@
       <c r="D317" t="s">
         <v>40</v>
       </c>
-      <c r="E317">
+      <c r="E317" s="1">
         <v>156250</v>
       </c>
       <c r="F317" t="s">
@@ -8145,7 +8158,7 @@
       <c r="D318" t="s">
         <v>40</v>
       </c>
-      <c r="E318">
+      <c r="E318" s="1">
         <v>31250</v>
       </c>
       <c r="F318" t="s">
@@ -8165,7 +8178,7 @@
       <c r="D319" t="s">
         <v>40</v>
       </c>
-      <c r="E319">
+      <c r="E319" s="1">
         <v>43750</v>
       </c>
       <c r="F319" t="s">
@@ -8185,7 +8198,7 @@
       <c r="D320" t="s">
         <v>40</v>
       </c>
-      <c r="E320">
+      <c r="E320" s="1">
         <v>18750</v>
       </c>
       <c r="F320" t="s">
@@ -8205,7 +8218,7 @@
       <c r="D321" t="s">
         <v>40</v>
       </c>
-      <c r="E321">
+      <c r="E321" s="1">
         <v>25000</v>
       </c>
       <c r="F321" t="s">
@@ -8225,7 +8238,7 @@
       <c r="D322" t="s">
         <v>40</v>
       </c>
-      <c r="E322">
+      <c r="E322" s="1">
         <v>20000</v>
       </c>
       <c r="F322" t="s">
@@ -8245,7 +8258,7 @@
       <c r="D323" t="s">
         <v>40</v>
       </c>
-      <c r="E323">
+      <c r="E323" s="1">
         <v>70000</v>
       </c>
       <c r="F323" t="s">
@@ -8265,7 +8278,7 @@
       <c r="D324" t="s">
         <v>40</v>
       </c>
-      <c r="E324">
+      <c r="E324" s="1">
         <v>31250</v>
       </c>
       <c r="F324" t="s">
@@ -8285,7 +8298,7 @@
       <c r="D325" t="s">
         <v>40</v>
       </c>
-      <c r="E325">
+      <c r="E325" s="1">
         <v>181250</v>
       </c>
       <c r="F325" t="s">
@@ -8305,7 +8318,7 @@
       <c r="D326" t="s">
         <v>71</v>
       </c>
-      <c r="E326">
+      <c r="E326" s="1">
         <v>293750</v>
       </c>
       <c r="F326" t="s">
@@ -8325,7 +8338,7 @@
       <c r="D327" t="s">
         <v>40</v>
       </c>
-      <c r="E327">
+      <c r="E327" s="1">
         <v>120000</v>
       </c>
       <c r="F327" t="s">
@@ -8345,7 +8358,7 @@
       <c r="D328" t="s">
         <v>71</v>
       </c>
-      <c r="E328">
+      <c r="E328" s="1">
         <v>450000</v>
       </c>
       <c r="F328" t="s">
@@ -8365,7 +8378,7 @@
       <c r="D329" t="s">
         <v>71</v>
       </c>
-      <c r="E329">
+      <c r="E329" s="1">
         <v>400000</v>
       </c>
       <c r="F329" t="s">
@@ -8385,7 +8398,7 @@
       <c r="D330" t="s">
         <v>71</v>
       </c>
-      <c r="E330">
+      <c r="E330" s="1">
         <v>375000</v>
       </c>
       <c r="F330" t="s">
@@ -8405,7 +8418,7 @@
       <c r="D331" t="s">
         <v>71</v>
       </c>
-      <c r="E331">
+      <c r="E331" s="1">
         <v>300000</v>
       </c>
       <c r="F331" t="s">
@@ -8425,7 +8438,7 @@
       <c r="D332" t="s">
         <v>71</v>
       </c>
-      <c r="E332">
+      <c r="E332" s="1">
         <v>325000</v>
       </c>
       <c r="F332" t="s">
@@ -8445,7 +8458,7 @@
       <c r="D333" t="s">
         <v>71</v>
       </c>
-      <c r="E333">
+      <c r="E333" s="1">
         <v>150000</v>
       </c>
       <c r="F333" t="s">
@@ -8465,7 +8478,7 @@
       <c r="D334" t="s">
         <v>353</v>
       </c>
-      <c r="E334">
+      <c r="E334" s="1">
         <v>50000</v>
       </c>
       <c r="F334" t="s">
@@ -8485,7 +8498,7 @@
       <c r="D335" t="s">
         <v>353</v>
       </c>
-      <c r="E335">
+      <c r="E335" s="1">
         <v>50000</v>
       </c>
       <c r="F335" t="s">
@@ -8505,7 +8518,7 @@
       <c r="D336" t="s">
         <v>40</v>
       </c>
-      <c r="E336">
+      <c r="E336" s="1">
         <v>75000</v>
       </c>
       <c r="F336" t="s">
@@ -8525,7 +8538,7 @@
       <c r="D337" t="s">
         <v>40</v>
       </c>
-      <c r="E337">
+      <c r="E337" s="1">
         <v>50000</v>
       </c>
       <c r="F337" t="s">
@@ -8545,7 +8558,7 @@
       <c r="D338" t="s">
         <v>40</v>
       </c>
-      <c r="E338">
+      <c r="E338" s="1">
         <v>2000</v>
       </c>
       <c r="F338" t="s">
@@ -8565,7 +8578,7 @@
       <c r="D339" t="s">
         <v>40</v>
       </c>
-      <c r="E339">
+      <c r="E339" s="1">
         <v>7000</v>
       </c>
       <c r="F339" t="s">
@@ -8585,7 +8598,7 @@
       <c r="D340" t="s">
         <v>40</v>
       </c>
-      <c r="E340">
+      <c r="E340" s="1">
         <v>150000</v>
       </c>
       <c r="F340" t="s">
@@ -8605,7 +8618,7 @@
       <c r="D341" t="s">
         <v>40</v>
       </c>
-      <c r="E341">
+      <c r="E341" s="1">
         <v>300000</v>
       </c>
       <c r="F341" t="s">
@@ -8625,7 +8638,7 @@
       <c r="D342" t="s">
         <v>40</v>
       </c>
-      <c r="E342">
+      <c r="E342" s="1">
         <v>93750</v>
       </c>
       <c r="F342" t="s">
@@ -8645,7 +8658,7 @@
       <c r="D343" t="s">
         <v>353</v>
       </c>
-      <c r="E343">
+      <c r="E343" s="1">
         <v>162500</v>
       </c>
       <c r="F343" t="s">
@@ -8665,7 +8678,7 @@
       <c r="D344" t="s">
         <v>40</v>
       </c>
-      <c r="E344">
+      <c r="E344" s="1">
         <v>118750</v>
       </c>
       <c r="F344" t="s">
@@ -8685,7 +8698,7 @@
       <c r="D345" t="s">
         <v>40</v>
       </c>
-      <c r="E345">
+      <c r="E345" s="1">
         <v>250000</v>
       </c>
       <c r="F345" t="s">
@@ -8705,7 +8718,7 @@
       <c r="D346" t="s">
         <v>353</v>
       </c>
-      <c r="E346">
+      <c r="E346" s="1">
         <v>31250</v>
       </c>
       <c r="F346" t="s">
@@ -8725,7 +8738,7 @@
       <c r="D347" t="s">
         <v>40</v>
       </c>
-      <c r="E347">
+      <c r="E347" s="1">
         <v>93750</v>
       </c>
       <c r="F347" t="s">
@@ -8745,7 +8758,7 @@
       <c r="D348" t="s">
         <v>40</v>
       </c>
-      <c r="E348">
+      <c r="E348" s="1">
         <v>93750</v>
       </c>
       <c r="F348" t="s">
@@ -8765,7 +8778,7 @@
       <c r="D349" t="s">
         <v>40</v>
       </c>
-      <c r="E349">
+      <c r="E349" s="1">
         <v>37500</v>
       </c>
       <c r="F349" t="s">
@@ -8785,7 +8798,7 @@
       <c r="D350" t="s">
         <v>40</v>
       </c>
-      <c r="E350">
+      <c r="E350" s="1">
         <v>6250</v>
       </c>
       <c r="F350" t="s">
@@ -8805,7 +8818,7 @@
       <c r="D351" t="s">
         <v>353</v>
       </c>
-      <c r="E351">
+      <c r="E351" s="1">
         <v>31250</v>
       </c>
       <c r="F351" t="s">
@@ -8825,7 +8838,7 @@
       <c r="D352" t="s">
         <v>40</v>
       </c>
-      <c r="E352">
+      <c r="E352" s="1">
         <v>37500</v>
       </c>
       <c r="F352" t="s">
@@ -8845,7 +8858,7 @@
       <c r="D353" t="s">
         <v>40</v>
       </c>
-      <c r="E353">
+      <c r="E353" s="1">
         <v>1875000</v>
       </c>
       <c r="F353" t="s">
@@ -8865,7 +8878,7 @@
       <c r="D354" t="s">
         <v>40</v>
       </c>
-      <c r="E354">
+      <c r="E354" s="1">
         <v>125000</v>
       </c>
       <c r="F354" t="s">
@@ -8885,7 +8898,7 @@
       <c r="D355" t="s">
         <v>374</v>
       </c>
-      <c r="E355">
+      <c r="E355" s="1">
         <v>712500</v>
       </c>
       <c r="F355" t="s">
@@ -8905,7 +8918,7 @@
       <c r="D356" t="s">
         <v>374</v>
       </c>
-      <c r="E356">
+      <c r="E356" s="1">
         <v>712500</v>
       </c>
       <c r="F356" t="s">
@@ -8925,7 +8938,7 @@
       <c r="D357" t="s">
         <v>40</v>
       </c>
-      <c r="E357">
+      <c r="E357" s="1">
         <v>22500</v>
       </c>
       <c r="F357" t="s">
@@ -8945,7 +8958,7 @@
       <c r="D358" t="s">
         <v>40</v>
       </c>
-      <c r="E358">
+      <c r="E358" s="1">
         <v>60033</v>
       </c>
       <c r="F358" t="s">
@@ -8965,7 +8978,7 @@
       <c r="D359" t="s">
         <v>68</v>
       </c>
-      <c r="E359">
+      <c r="E359" s="1">
         <v>1000000</v>
       </c>
       <c r="F359" t="s">
@@ -8985,7 +8998,7 @@
       <c r="D360" t="s">
         <v>68</v>
       </c>
-      <c r="E360">
+      <c r="E360" s="1">
         <v>7600000</v>
       </c>
       <c r="F360" t="s">
@@ -9005,7 +9018,7 @@
       <c r="D361" t="s">
         <v>68</v>
       </c>
-      <c r="E361">
+      <c r="E361" s="1">
         <v>7500000</v>
       </c>
       <c r="F361" t="s">
@@ -9025,7 +9038,7 @@
       <c r="D362" t="s">
         <v>9</v>
       </c>
-      <c r="E362">
+      <c r="E362" s="1">
         <v>17500000</v>
       </c>
       <c r="F362" t="s">
@@ -9045,7 +9058,7 @@
       <c r="D363" t="s">
         <v>9</v>
       </c>
-      <c r="E363">
+      <c r="E363" s="1">
         <v>20000000</v>
       </c>
       <c r="F363" t="s">
@@ -9065,7 +9078,7 @@
       <c r="D364" t="s">
         <v>9</v>
       </c>
-      <c r="E364">
+      <c r="E364" s="1">
         <v>10000000</v>
       </c>
       <c r="F364" t="s">
@@ -9085,7 +9098,7 @@
       <c r="D365" t="s">
         <v>9</v>
       </c>
-      <c r="E365">
+      <c r="E365" s="1">
         <v>7500000</v>
       </c>
       <c r="F365" t="s">
@@ -9105,7 +9118,7 @@
       <c r="D366" t="s">
         <v>9</v>
       </c>
-      <c r="E366">
+      <c r="E366" s="1">
         <v>10000000</v>
       </c>
       <c r="F366" t="s">
@@ -9125,7 +9138,7 @@
       <c r="D367" t="s">
         <v>9</v>
       </c>
-      <c r="E367">
+      <c r="E367" s="1">
         <v>25000000</v>
       </c>
       <c r="F367" t="s">
@@ -9145,7 +9158,7 @@
       <c r="D368" t="s">
         <v>40</v>
       </c>
-      <c r="E368">
+      <c r="E368" s="1">
         <v>65000</v>
       </c>
       <c r="F368" t="s">
@@ -9165,7 +9178,7 @@
       <c r="D369" t="s">
         <v>40</v>
       </c>
-      <c r="E369">
+      <c r="E369" s="1">
         <v>33000</v>
       </c>
       <c r="F369" t="s">
@@ -9185,7 +9198,7 @@
       <c r="D370" t="s">
         <v>353</v>
       </c>
-      <c r="E370">
+      <c r="E370" s="1">
         <v>25000</v>
       </c>
       <c r="F370" t="s">
@@ -9205,7 +9218,7 @@
       <c r="D371" t="s">
         <v>353</v>
       </c>
-      <c r="E371">
+      <c r="E371" s="1">
         <v>750000</v>
       </c>
       <c r="F371" t="s">
@@ -9225,7 +9238,7 @@
       <c r="D372" t="s">
         <v>392</v>
       </c>
-      <c r="E372">
+      <c r="E372" s="1">
         <v>750000</v>
       </c>
       <c r="F372" t="s">
@@ -9245,7 +9258,7 @@
       <c r="D373" t="s">
         <v>392</v>
       </c>
-      <c r="E373">
+      <c r="E373" s="1">
         <v>750000</v>
       </c>
       <c r="F373" t="s">
@@ -9265,7 +9278,7 @@
       <c r="D374" t="s">
         <v>392</v>
       </c>
-      <c r="E374">
+      <c r="E374" s="1">
         <v>250000</v>
       </c>
       <c r="F374" t="s">
@@ -9285,7 +9298,7 @@
       <c r="D375" t="s">
         <v>392</v>
       </c>
-      <c r="E375">
+      <c r="E375" s="1">
         <v>350000</v>
       </c>
       <c r="F375" t="s">
@@ -9305,7 +9318,7 @@
       <c r="D376" t="s">
         <v>392</v>
       </c>
-      <c r="E376">
+      <c r="E376" s="1">
         <v>275000</v>
       </c>
       <c r="F376" t="s">
@@ -9325,7 +9338,7 @@
       <c r="D377" t="s">
         <v>392</v>
       </c>
-      <c r="E377">
+      <c r="E377" s="1">
         <v>500000</v>
       </c>
       <c r="F377" t="s">
@@ -9345,7 +9358,7 @@
       <c r="D378" t="s">
         <v>392</v>
       </c>
-      <c r="E378">
+      <c r="E378" s="1">
         <v>500000</v>
       </c>
       <c r="F378" t="s">
@@ -9365,7 +9378,7 @@
       <c r="D379" t="s">
         <v>392</v>
       </c>
-      <c r="E379">
+      <c r="E379" s="1">
         <v>325000</v>
       </c>
       <c r="F379" t="s">
@@ -9385,7 +9398,7 @@
       <c r="D380" t="s">
         <v>392</v>
       </c>
-      <c r="E380">
+      <c r="E380" s="1">
         <v>750000</v>
       </c>
       <c r="F380" t="s">
@@ -9405,7 +9418,7 @@
       <c r="D381" t="s">
         <v>392</v>
       </c>
-      <c r="E381">
+      <c r="E381" s="1">
         <v>650000</v>
       </c>
       <c r="F381" t="s">
@@ -9425,7 +9438,7 @@
       <c r="D382" t="s">
         <v>392</v>
       </c>
-      <c r="E382">
+      <c r="E382" s="1">
         <v>500000</v>
       </c>
       <c r="F382" t="s">
@@ -9445,7 +9458,7 @@
       <c r="D383" t="s">
         <v>392</v>
       </c>
-      <c r="E383">
+      <c r="E383" s="1">
         <v>500000</v>
       </c>
       <c r="F383" t="s">
@@ -9465,7 +9478,7 @@
       <c r="D384" t="s">
         <v>392</v>
       </c>
-      <c r="E384">
+      <c r="E384" s="1">
         <v>500000</v>
       </c>
       <c r="F384" t="s">
@@ -9485,7 +9498,7 @@
       <c r="D385" t="s">
         <v>392</v>
       </c>
-      <c r="E385">
+      <c r="E385" s="1">
         <v>500000</v>
       </c>
       <c r="F385" t="s">
@@ -9505,7 +9518,7 @@
       <c r="D386" t="s">
         <v>392</v>
       </c>
-      <c r="E386">
+      <c r="E386" s="1">
         <v>500000</v>
       </c>
       <c r="F386" t="s">
@@ -9525,7 +9538,7 @@
       <c r="D387" t="s">
         <v>392</v>
       </c>
-      <c r="E387">
+      <c r="E387" s="1">
         <v>500000</v>
       </c>
       <c r="F387" t="s">
@@ -9545,7 +9558,7 @@
       <c r="D388" t="s">
         <v>392</v>
       </c>
-      <c r="E388">
+      <c r="E388" s="1">
         <v>600000</v>
       </c>
       <c r="F388" t="s">
@@ -9565,7 +9578,7 @@
       <c r="D389" t="s">
         <v>353</v>
       </c>
-      <c r="E389">
+      <c r="E389" s="1">
         <v>150000</v>
       </c>
       <c r="F389" t="s">
@@ -9585,7 +9598,7 @@
       <c r="D390" t="s">
         <v>353</v>
       </c>
-      <c r="E390">
+      <c r="E390" s="1">
         <v>200000</v>
       </c>
       <c r="F390" t="s">
@@ -9605,7 +9618,7 @@
       <c r="D391" t="s">
         <v>353</v>
       </c>
-      <c r="E391">
+      <c r="E391" s="1">
         <v>175000</v>
       </c>
       <c r="F391" t="s">
@@ -9625,7 +9638,7 @@
       <c r="D392" t="s">
         <v>353</v>
       </c>
-      <c r="E392">
+      <c r="E392" s="1">
         <v>125000</v>
       </c>
       <c r="F392" t="s">
@@ -9645,7 +9658,7 @@
       <c r="D393" t="s">
         <v>353</v>
       </c>
-      <c r="E393">
+      <c r="E393" s="1">
         <v>150000</v>
       </c>
       <c r="F393" t="s">
@@ -9665,7 +9678,7 @@
       <c r="D394" t="s">
         <v>353</v>
       </c>
-      <c r="E394">
+      <c r="E394" s="1">
         <v>200000</v>
       </c>
       <c r="F394" t="s">
@@ -9685,7 +9698,7 @@
       <c r="D395" t="s">
         <v>353</v>
       </c>
-      <c r="E395">
+      <c r="E395" s="1">
         <v>200000</v>
       </c>
       <c r="F395" t="s">
@@ -9705,7 +9718,7 @@
       <c r="D396" t="s">
         <v>353</v>
       </c>
-      <c r="E396">
+      <c r="E396" s="1">
         <v>150000</v>
       </c>
       <c r="F396" t="s">
@@ -9725,7 +9738,7 @@
       <c r="D397" t="s">
         <v>353</v>
       </c>
-      <c r="E397">
+      <c r="E397" s="1">
         <v>100000</v>
       </c>
       <c r="F397" t="s">
@@ -9745,7 +9758,7 @@
       <c r="D398" t="s">
         <v>353</v>
       </c>
-      <c r="E398">
+      <c r="E398" s="1">
         <v>100000</v>
       </c>
       <c r="F398" t="s">
@@ -9765,7 +9778,7 @@
       <c r="D399" t="s">
         <v>353</v>
       </c>
-      <c r="E399">
+      <c r="E399" s="1">
         <v>125000</v>
       </c>
       <c r="F399" t="s">
@@ -9785,7 +9798,7 @@
       <c r="D400" t="s">
         <v>421</v>
       </c>
-      <c r="E400">
+      <c r="E400" s="1">
         <v>250000</v>
       </c>
       <c r="F400" t="s">
@@ -9805,7 +9818,7 @@
       <c r="D401" t="s">
         <v>353</v>
       </c>
-      <c r="E401">
+      <c r="E401" s="1">
         <v>20000000</v>
       </c>
       <c r="F401" t="s">
@@ -9825,7 +9838,7 @@
       <c r="D402" t="s">
         <v>68</v>
       </c>
-      <c r="E402">
+      <c r="E402" s="1">
         <v>20000000</v>
       </c>
       <c r="F402" t="s">
@@ -9845,7 +9858,7 @@
       <c r="D403" t="s">
         <v>68</v>
       </c>
-      <c r="E403">
+      <c r="E403" s="1">
         <v>50000000</v>
       </c>
       <c r="F403" t="s">
@@ -9865,7 +9878,7 @@
       <c r="D404" t="s">
         <v>68</v>
       </c>
-      <c r="E404">
+      <c r="E404" s="1">
         <v>28000000</v>
       </c>
       <c r="F404" t="s">
@@ -9885,7 +9898,7 @@
       <c r="D405" t="s">
         <v>68</v>
       </c>
-      <c r="E405">
+      <c r="E405" s="1">
         <v>22400000</v>
       </c>
       <c r="F405" t="s">
@@ -9905,7 +9918,7 @@
       <c r="D406" t="s">
         <v>68</v>
       </c>
-      <c r="E406">
+      <c r="E406" s="1">
         <v>15400000</v>
       </c>
       <c r="F406" t="s">
@@ -9925,7 +9938,7 @@
       <c r="D407" t="s">
         <v>68</v>
       </c>
-      <c r="E407">
+      <c r="E407" s="1">
         <v>32200000</v>
       </c>
       <c r="F407" t="s">
@@ -9945,7 +9958,7 @@
       <c r="D408" t="s">
         <v>68</v>
       </c>
-      <c r="E408">
+      <c r="E408" s="1">
         <v>29400000</v>
       </c>
       <c r="F408" t="s">
@@ -9965,7 +9978,7 @@
       <c r="D409" t="s">
         <v>68</v>
       </c>
-      <c r="E409">
+      <c r="E409" s="1">
         <v>59000000</v>
       </c>
       <c r="F409" t="s">
@@ -9985,7 +9998,7 @@
       <c r="D410" t="s">
         <v>68</v>
       </c>
-      <c r="E410">
+      <c r="E410" s="1">
         <v>22400000</v>
       </c>
       <c r="F410" t="s">
@@ -10005,7 +10018,7 @@
       <c r="D411" t="s">
         <v>68</v>
       </c>
-      <c r="E411">
+      <c r="E411" s="1">
         <v>27300000</v>
       </c>
       <c r="F411" t="s">
@@ -10025,7 +10038,7 @@
       <c r="D412" t="s">
         <v>68</v>
       </c>
-      <c r="E412">
+      <c r="E412" s="1">
         <v>27300000</v>
       </c>
       <c r="F412" t="s">
@@ -10045,7 +10058,7 @@
       <c r="D413" t="s">
         <v>421</v>
       </c>
-      <c r="E413">
+      <c r="E413" s="1">
         <v>1000000</v>
       </c>
       <c r="F413" t="s">
@@ -10065,7 +10078,7 @@
       <c r="D414" t="s">
         <v>40</v>
       </c>
-      <c r="E414">
+      <c r="E414" s="1">
         <v>7500</v>
       </c>
       <c r="F414" t="s">
@@ -10085,7 +10098,7 @@
       <c r="D415" t="s">
         <v>40</v>
       </c>
-      <c r="E415">
+      <c r="E415" s="1">
         <v>53300</v>
       </c>
       <c r="F415" t="s">
@@ -10105,7 +10118,7 @@
       <c r="D416" t="s">
         <v>40</v>
       </c>
-      <c r="E416">
+      <c r="E416" s="1">
         <v>32500</v>
       </c>
       <c r="F416" t="s">
@@ -10125,7 +10138,7 @@
       <c r="D417" t="s">
         <v>40</v>
       </c>
-      <c r="E417">
+      <c r="E417" s="1">
         <v>84500</v>
       </c>
       <c r="F417" t="s">
@@ -10145,7 +10158,7 @@
       <c r="D418" t="s">
         <v>40</v>
       </c>
-      <c r="E418">
+      <c r="E418" s="1">
         <v>26000</v>
       </c>
       <c r="F418" t="s">
@@ -10165,7 +10178,7 @@
       <c r="D419" t="s">
         <v>40</v>
       </c>
-      <c r="E419">
+      <c r="E419" s="1">
         <v>32500</v>
       </c>
       <c r="F419" t="s">
@@ -10185,7 +10198,7 @@
       <c r="D420" t="s">
         <v>40</v>
       </c>
-      <c r="E420">
+      <c r="E420" s="1">
         <v>45500</v>
       </c>
       <c r="F420" t="s">
@@ -10205,7 +10218,7 @@
       <c r="D421" t="s">
         <v>40</v>
       </c>
-      <c r="E421">
+      <c r="E421" s="1">
         <v>9750</v>
       </c>
       <c r="F421" t="s">
@@ -10225,7 +10238,7 @@
       <c r="D422" t="s">
         <v>40</v>
       </c>
-      <c r="E422">
+      <c r="E422" s="1">
         <v>31200</v>
       </c>
       <c r="F422" t="s">
@@ -10245,7 +10258,7 @@
       <c r="D423" t="s">
         <v>40</v>
       </c>
-      <c r="E423">
+      <c r="E423" s="1">
         <v>32500</v>
       </c>
       <c r="F423" t="s">
@@ -10265,7 +10278,7 @@
       <c r="D424" t="s">
         <v>40</v>
       </c>
-      <c r="E424">
+      <c r="E424" s="1">
         <v>32500</v>
       </c>
       <c r="F424" t="s">
@@ -10285,7 +10298,7 @@
       <c r="D425" t="s">
         <v>40</v>
       </c>
-      <c r="E425">
+      <c r="E425" s="1">
         <v>19500</v>
       </c>
       <c r="F425" t="s">
@@ -10305,7 +10318,7 @@
       <c r="D426" t="s">
         <v>40</v>
       </c>
-      <c r="E426">
+      <c r="E426" s="1">
         <v>13000</v>
       </c>
       <c r="F426" t="s">
@@ -10325,7 +10338,7 @@
       <c r="D427" t="s">
         <v>40</v>
       </c>
-      <c r="E427">
+      <c r="E427" s="1">
         <v>9750</v>
       </c>
       <c r="F427" t="s">
@@ -10345,7 +10358,7 @@
       <c r="D428" t="s">
         <v>40</v>
       </c>
-      <c r="E428">
+      <c r="E428" s="1">
         <v>19500</v>
       </c>
       <c r="F428" t="s">
@@ -10365,7 +10378,7 @@
       <c r="D429" t="s">
         <v>40</v>
       </c>
-      <c r="E429">
+      <c r="E429" s="1">
         <v>9750</v>
       </c>
       <c r="F429" t="s">
@@ -10385,7 +10398,7 @@
       <c r="D430" t="s">
         <v>40</v>
       </c>
-      <c r="E430">
+      <c r="E430" s="1">
         <v>9750</v>
       </c>
       <c r="F430" t="s">
@@ -10405,7 +10418,7 @@
       <c r="D431" t="s">
         <v>40</v>
       </c>
-      <c r="E431">
+      <c r="E431" s="1">
         <v>15600</v>
       </c>
       <c r="F431" t="s">
@@ -10425,7 +10438,7 @@
       <c r="D432" t="s">
         <v>40</v>
       </c>
-      <c r="E432">
+      <c r="E432" s="1">
         <v>32500</v>
       </c>
       <c r="F432" t="s">
@@ -10445,7 +10458,7 @@
       <c r="D433" t="s">
         <v>40</v>
       </c>
-      <c r="E433">
+      <c r="E433" s="1">
         <v>32500</v>
       </c>
       <c r="F433" t="s">
@@ -10465,7 +10478,7 @@
       <c r="D434" t="s">
         <v>40</v>
       </c>
-      <c r="E434">
+      <c r="E434" s="1">
         <v>32500</v>
       </c>
       <c r="F434" t="s">
@@ -10485,7 +10498,7 @@
       <c r="D435" t="s">
         <v>40</v>
       </c>
-      <c r="E435">
+      <c r="E435" s="1">
         <v>1625000</v>
       </c>
       <c r="F435" t="s">
@@ -10505,7 +10518,7 @@
       <c r="D436" t="s">
         <v>40</v>
       </c>
-      <c r="E436">
+      <c r="E436" s="1">
         <v>325000</v>
       </c>
       <c r="F436" t="s">
@@ -10525,7 +10538,7 @@
       <c r="D437" t="s">
         <v>40</v>
       </c>
-      <c r="E437">
+      <c r="E437" s="1">
         <v>19500000</v>
       </c>
       <c r="F437" t="s">
@@ -10545,7 +10558,7 @@
       <c r="D438" t="s">
         <v>40</v>
       </c>
-      <c r="E438">
+      <c r="E438" s="1">
         <v>19500000</v>
       </c>
       <c r="F438" t="s">
@@ -10565,7 +10578,7 @@
       <c r="D439" t="s">
         <v>31</v>
       </c>
-      <c r="E439">
+      <c r="E439" s="1">
         <v>3250000</v>
       </c>
       <c r="F439" t="s">
@@ -10585,7 +10598,7 @@
       <c r="D440" t="s">
         <v>31</v>
       </c>
-      <c r="E440">
+      <c r="E440" s="1">
         <v>3900000</v>
       </c>
       <c r="F440" t="s">
@@ -10605,7 +10618,7 @@
       <c r="D441" t="s">
         <v>31</v>
       </c>
-      <c r="E441">
+      <c r="E441" s="1">
         <v>3900000</v>
       </c>
       <c r="F441" t="s">
@@ -10625,7 +10638,7 @@
       <c r="D442" t="s">
         <v>31</v>
       </c>
-      <c r="E442">
+      <c r="E442" s="1">
         <v>5600000</v>
       </c>
       <c r="F442" t="s">
@@ -10645,7 +10658,7 @@
       <c r="D443" t="s">
         <v>31</v>
       </c>
-      <c r="E443">
+      <c r="E443" s="1">
         <v>8400000</v>
       </c>
       <c r="F443" t="s">
@@ -10665,7 +10678,7 @@
       <c r="D444" t="s">
         <v>31</v>
       </c>
-      <c r="E444">
+      <c r="E444" s="1">
         <v>7000000</v>
       </c>
       <c r="F444" t="s">
@@ -10685,7 +10698,7 @@
       <c r="D445" t="s">
         <v>31</v>
       </c>
-      <c r="E445">
+      <c r="E445" s="1">
         <v>9100000</v>
       </c>
       <c r="F445" t="s">
@@ -10705,7 +10718,7 @@
       <c r="D446" t="s">
         <v>31</v>
       </c>
-      <c r="E446">
+      <c r="E446" s="1">
         <v>10500000</v>
       </c>
       <c r="F446" t="s">
@@ -10725,7 +10738,7 @@
       <c r="D447" t="s">
         <v>31</v>
       </c>
-      <c r="E447">
+      <c r="E447" s="1">
         <v>10500000</v>
       </c>
       <c r="F447" t="s">
@@ -10745,7 +10758,7 @@
       <c r="D448" t="s">
         <v>31</v>
       </c>
-      <c r="E448">
+      <c r="E448" s="1">
         <v>14000000</v>
       </c>
       <c r="F448" t="s">
@@ -10765,7 +10778,7 @@
       <c r="D449" t="s">
         <v>31</v>
       </c>
-      <c r="E449">
+      <c r="E449" s="1">
         <v>14000000</v>
       </c>
       <c r="F449" t="s">
@@ -10785,7 +10798,7 @@
       <c r="D450" t="s">
         <v>31</v>
       </c>
-      <c r="E450">
+      <c r="E450" s="1">
         <v>25200000</v>
       </c>
       <c r="F450" t="s">
@@ -10805,7 +10818,7 @@
       <c r="D451" t="s">
         <v>421</v>
       </c>
-      <c r="E451">
+      <c r="E451" s="1">
         <v>250000</v>
       </c>
       <c r="F451" t="s">
@@ -10825,7 +10838,7 @@
       <c r="D452" t="s">
         <v>68</v>
       </c>
-      <c r="E452">
+      <c r="E452" s="1">
         <v>0</v>
       </c>
       <c r="F452" t="s">
@@ -10845,7 +10858,7 @@
       <c r="D453" t="s">
         <v>40</v>
       </c>
-      <c r="E453">
+      <c r="E453" s="1">
         <v>7500</v>
       </c>
       <c r="F453" t="s">
@@ -10865,7 +10878,7 @@
       <c r="D454" t="s">
         <v>40</v>
       </c>
-      <c r="E454">
+      <c r="E454" s="1">
         <v>7500</v>
       </c>
       <c r="F454" t="s">
